--- a/sampleprojects/CorporateTax/excel/states/MA_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/MA_corp.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t>DT: Determine MA Filing Requirement</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Meets economic nexus threshold ($500K gross receipts); result.ma_gross_receipts is greater than or equal to result.ma_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.ma_gross_receipts &gt;= result.ma_economic_nexus_threshold</t>
+    <t>ma_result.gross_receipts &gt;= ma_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>set result.ma_has_nexus = true;</t>
+    <t>set ma_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,7 +97,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.ma_has_nexus = false; set result.ma_tax_liability = 0.0;</t>
+    <t>set ma_result.has_nexus = false; set ma_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate MA Income Adjustments</t>
@@ -115,19 +115,19 @@
     <t>Has Massachusetts nexus</t>
   </si>
   <si>
-    <t>result.ma_has_nexus is equal to true</t>
+    <t>ma_result.has_nexus is equal to true</t>
   </si>
   <si>
     <t>Calculate Massachusetts state additions and subtractions; Calculate state-specific income adjustments</t>
   </si>
   <si>
-    <t>set result.ma_state_additions = 0.0; if result.ma_us_interest_income != 0.0 then set result.ma_state_additions = result.ma_state_additions + result.ma_us_interest_income; endif set result.ma_state_subtractions = 0.0; if result.ma_municipal_interest != 0.0 then set result.ma_state_subtractions = result.ma_state_subtractions + result.ma_municipal_interest; endif if result.ma_qualified_dividend_deduction != 0.0 then set result.ma_state_subtractions = result.ma_state_subtractions + result.ma_qualified_dividend_deduction; endif add (("Massachusetts additions: $" + string value of (result.ma_state_additions)) + ", subtractions: $") + string value of (result.ma_state_subtractions) to job.audit_trail;</t>
+    <t>set ma_result.state_additions = 0.0; if ma_result.us_interest_income != 0.0 then set ma_result.state_additions = ma_result.state_additions + ma_result.us_interest_income; endif set ma_result.state_subtractions = 0.0; if ma_result.municipal_interest != 0.0 then set ma_result.state_subtractions = ma_result.state_subtractions + ma_result.municipal_interest; endif if ma_result.qualified_dividend_deduction != 0.0 then set ma_result.state_subtractions = ma_result.state_subtractions + ma_result.qualified_dividend_deduction; endif add (("Massachusetts additions: $" + string value of (ma_result.state_additions)) + ", subtractions: $") + string value of (ma_result.state_subtractions) to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no adjustments</t>
   </si>
   <si>
-    <t>set result.ma_state_additions = 0.0; set result.ma_state_subtractions = 0.0;</t>
+    <t>set ma_result.state_additions = 0.0; set ma_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate MA State Tax</t>
@@ -145,19 +145,19 @@
     <t>Has positive taxable income; result.ma_apportioned_income is greater than 0</t>
   </si>
   <si>
-    <t>result.ma_apportioned_income &gt; 0.0</t>
+    <t>ma_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Calculate Massachusetts corporate tax (flat rate 8.0%); Apply Massachusetts 8.0% flat rate</t>
   </si>
   <si>
-    <t>set result.ma_taxable_income = the maximum of (result.ma_apportioned_income + result.ma_state_additions - result.ma_state_subtractions) and (0.0); set result.ma_tax_liability = the maximum of (result.ma_taxable_income * result.ma_corp_tax_rate - result.ma_state_credits) and (0.0); set result.ma_refund_or_owed = result.ma_estimated_payments - result.ma_tax_liability; add "Massachusetts taxable income: $" + string value of (result.ma_taxable_income) to job.audit_trail; add "Massachusetts tax liability (8.0%): $" + string value of (result.ma_tax_liability) to job.audit_trail;</t>
+    <t>set ma_result.taxable_income = the maximum of (ma_result.apportioned_income + ma_result.state_additions - ma_result.state_subtractions) and (0.0); set ma_result.tax_liability = the maximum of (ma_result.taxable_income * ma_result.corp_tax_rate - ma_result.state_credits) and (0.0); set ma_result.refund_or_owed = ma_result.estimated_payments - ma_result.tax_liability; add "Massachusetts taxable income: $" + string value of (ma_result.taxable_income) to job.audit_trail; add "Massachusetts tax liability (8.0%): $" + string value of (ma_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability</t>
   </si>
   <si>
-    <t>set result.ma_taxable_income = 0.0; set result.ma_tax_liability = 0.0;</t>
+    <t>set ma_result.taxable_income = 0.0; set ma_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -205,10 +205,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>ma_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -238,115 +238,85 @@
     <t>MA economic nexus gross receipts threshold - $500,000</t>
   </si>
   <si>
+    <t>state_tax_rate</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>MA corporate excise tax rate - 8% flat rate (M.G.L. c. 63 § 39)</t>
+  </si>
+  <si>
+    <t>transaction_threshold</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>MA economic nexus transaction count threshold - 200</t>
+  </si>
+  <si>
+    <t>ma_result</t>
+  </si>
+  <si>
+    <t>(15 attributes)</t>
+  </si>
+  <si>
+    <t>apportioned_income</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>Declared from decision-table usage; referenced by MA but never declared (campaign #948 Phase 1)</t>
+  </si>
+  <si>
+    <t>corp_tax_rate</t>
+  </si>
+  <si>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>qualified_dividend_deduction</t>
+  </si>
+  <si>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
     <t>state_additions</t>
   </si>
   <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>MA-specific additions: federal interest, IRC 199A addback, bonus depreciation, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>Massachusetts state code</t>
-  </si>
-  <si>
     <t>state_credits</t>
   </si>
   <si>
-    <t>MA tax credits: Economic Development Incentive Program (EDIP), R&amp;D, film, etc.</t>
-  </si>
-  <si>
     <t>state_subtractions</t>
   </si>
   <si>
-    <t>MA-specific subtractions: municipal interest, state taxes, state NOL, etc.</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
-    <t>0.080</t>
-  </si>
-  <si>
-    <t>MA corporate excise tax rate - 8% flat rate (M.G.L. c. 63 § 39)</t>
-  </si>
-  <si>
-    <t>transaction_threshold</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>MA economic nexus transaction count threshold - 200</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(15 attributes)</t>
-  </si>
-  <si>
-    <t>ma_apportioned_income</t>
-  </si>
-  <si>
-    <t>Declared from decision-table usage; referenced by MA but never declared (campaign #948 Phase 1)</t>
-  </si>
-  <si>
-    <t>ma_corp_tax_rate</t>
-  </si>
-  <si>
-    <t>ma_economic_nexus_threshold</t>
-  </si>
-  <si>
-    <t>ma_estimated_payments</t>
-  </si>
-  <si>
-    <t>ma_gross_receipts</t>
-  </si>
-  <si>
-    <t>ma_has_nexus</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>ma_municipal_interest</t>
-  </si>
-  <si>
-    <t>ma_qualified_dividend_deduction</t>
-  </si>
-  <si>
-    <t>ma_refund_or_owed</t>
-  </si>
-  <si>
-    <t>ma_state_additions</t>
-  </si>
-  <si>
-    <t>ma_state_credits</t>
-  </si>
-  <si>
-    <t>ma_state_subtractions</t>
-  </si>
-  <si>
-    <t>ma_tax_liability</t>
-  </si>
-  <si>
-    <t>ma_taxable_income</t>
-  </si>
-  <si>
-    <t>ma_us_interest_income</t>
+    <t>tax_liability</t>
+  </si>
+  <si>
+    <t>taxable_income</t>
+  </si>
+  <si>
+    <t>us_interest_income</t>
   </si>
 </sst>
 </file>
@@ -2698,14 +2668,14 @@
       <c r="B7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>65</v>
+      <c r="C7" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
@@ -2714,7 +2684,7 @@
         <v>67</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -2733,194 +2703,194 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="A8" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="B8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>67</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="I10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="H10" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="9" t="s">
+      <c r="H11" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="C12" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="H12" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>70</v>
@@ -2929,7 +2899,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>8</v>
@@ -2938,7 +2908,7 @@
         <v>67</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>8</v>
@@ -2961,16 +2931,16 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>70</v>
+        <v>88</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>8</v>
@@ -2979,7 +2949,7 @@
         <v>67</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>8</v>
@@ -3002,7 +2972,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>70</v>
@@ -3011,7 +2981,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>8</v>
@@ -3020,7 +2990,7 @@
         <v>67</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>8</v>
@@ -3043,7 +3013,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>70</v>
@@ -3052,7 +3022,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>8</v>
@@ -3061,7 +3031,7 @@
         <v>67</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>8</v>
@@ -3084,7 +3054,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>70</v>
@@ -3093,7 +3063,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>8</v>
@@ -3102,7 +3072,7 @@
         <v>67</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>8</v>
@@ -3125,16 +3095,16 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>99</v>
+        <v>94</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>8</v>
@@ -3143,7 +3113,7 @@
         <v>67</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>8</v>
@@ -3166,7 +3136,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>70</v>
@@ -3175,7 +3145,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>8</v>
@@ -3184,7 +3154,7 @@
         <v>67</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>8</v>
@@ -3207,7 +3177,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>70</v>
@@ -3216,7 +3186,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>8</v>
@@ -3225,7 +3195,7 @@
         <v>67</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>8</v>
@@ -3248,7 +3218,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>70</v>
@@ -3257,7 +3227,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>8</v>
@@ -3266,7 +3236,7 @@
         <v>67</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>8</v>
@@ -3289,7 +3259,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>70</v>
@@ -3298,7 +3268,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>8</v>
@@ -3307,7 +3277,7 @@
         <v>67</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>8</v>
@@ -3330,7 +3300,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>70</v>
@@ -3339,7 +3309,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>8</v>
@@ -3348,7 +3318,7 @@
         <v>67</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>8</v>
@@ -3363,170 +3333,6 @@
         <v>8</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M27" s="7" t="s">
         <v>8</v>
       </c>
     </row>
